--- a/src/main/resources/espacios/0 Step/0 - Questions.xlsx
+++ b/src/main/resources/espacios/0 Step/0 - Questions.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="29"/>
   </bookViews>
   <sheets>
     <sheet name="1 How" sheetId="1" state="visible" r:id="rId3"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5458" uniqueCount="3856">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5491" uniqueCount="3856">
   <si>
     <t xml:space="preserve">How big...?</t>
   </si>
@@ -402,6 +402,741 @@
     <t xml:space="preserve">haʊ ˈsɪmpəl...?</t>
   </si>
   <si>
+    <t xml:space="preserve">How affordable...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan asequible...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ əˈfɔrdəbəl...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How anxious...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan ansioso...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈæŋkʃəs...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How boring...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan aburrido...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈbɔrɪŋ...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How capable...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan capaz...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈkeɪpəbəl...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How confident...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan seguro/confidente...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈkɑnfədənt...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How confusing...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan confuso...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ kənˈfjuzɪŋ...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How curious...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan curioso...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈkjʊriəs...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How dark...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan oscuro...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ dɑrk...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How disappointed...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan decepcionado...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˌdɪsəˈpɔɪntɪd...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How distracted...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan distraído...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ dɪˈstræktɪd...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How embarrassed...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan avergonzado...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ɪmˈbɛrəst...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How energetic...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan enérgico...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˌɛnərˈʤɛtɪk...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How experienced...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan experimentado...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ɪkˈspɪriənst...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How extroverted...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan extrovertido...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈɛkstrəˌvɜrtɪd...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How focused...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan concentrado...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈfoʊkəst...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How friendly...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan amigable...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈfrɛndli...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How frustrated...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan frustrado...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈfrʌˌstreɪtəd...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How grateful...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan agradecido...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈɡreɪtfəl...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How hopeful...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan esperanzado...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈhoʊpfəl...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How hungry...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan hambriento...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈhʌŋɡri...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How inspired...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan inspirado...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ɪnˈspaɪərd...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How interesting...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan interesante...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈɪntrəstɪŋ...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How introverted...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan introvertido...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈɪntroʊˌvɜrtɪd...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How jealous...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan celoso...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈʤɛləs...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How late...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan tarde...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ leɪt...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How lazy...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan perezoso...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈleɪzi...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How likely...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan probable...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈlaɪkli...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto tiempo...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan fuerte (de volumen)...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How motivated...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan motivado...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈmoʊtəˌveɪtəd...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How nervous...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan nervioso...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈnɜrvəs...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How optimistic...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan optimista...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˌɑptəˈmɪstɪk...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How overpriced...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan sobrevalorado/caro...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈoʊvərˌpraɪst...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How overwhelmed...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan abrumado...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˌoʊvərˈwɛlmd...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How patient...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan paciente...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈpeɪʃənt...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How pessimistic...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan pesimista...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˌpɛsəˈmɪstɪk...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How possible...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan posible...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈpɑsəbəl...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How productive...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan productivo...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ prəˈdʌktɪv...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How proud...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan orgulloso...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ praʊd...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan silencioso...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How relieved...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan aliviado...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ rɪˈlivd...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How scared...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan asustado...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ skɛrd...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan poco profundo...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How shy...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan tímido...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ʃaɪ...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How skilled...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan hábil...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ skɪld...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How sleepy...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan somnoliento...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈslipi...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How sociable...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan sociable...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈsoʊʃəbəl...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How soon...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan pronto...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ sun...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How sore...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan adolorido...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ sɔr...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How strong...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan fuerte...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ strɔŋ...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How surprised...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan sorprendido...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ sərˈpraɪzd...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How sweaty...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan sudoroso...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈswɛti...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How talkative...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan hablador...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈtɔkətɪv...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How thirsty...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan sediento...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈθɜrsti...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How warm...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan cálido...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ wɔrm...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How weak...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan débil...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ wik...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How wide...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan ancho...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ waɪd...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How accessible...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan accesible...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ækˈsɛsəbəl...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How adaptable...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan adaptable...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ əˈdæptəbəl...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How challenging...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan desafiante...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈʧælənʤɪŋ...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How clear...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan claro...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ klɪr...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How convenient...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan conveniente...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ kənˈvinjənt...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How critical...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan crítico...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈkrɪtɪkəl...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How crucial...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan crucial...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈkruʃəl...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How customizable...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan personalizable...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈkʌstəˌmaɪzəbᵊl...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How demanding...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan exigente...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ dɪˈmændɪŋ...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How durable...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan duradero...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈdʊrəbəl...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How effective...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan efectivo...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ɪˈfɛktɪv...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How efficient...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan eficiente...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ɪˈfɪʃənt...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How essential...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan esencial...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ɪˈsɛnʃəl...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How feasible...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan factible...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈfizəbəl...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How flexible...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan flexible...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈflɛksəbəl...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How influential...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan influyente...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˌɪnfluˈɛnʧəl...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How noticeable...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan notable...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈnoʊtəsəbəl...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How relevant...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan relevante...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈrɛləvənt...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How reliable...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan confiable...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ rɪˈlaɪəbəl...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How resistant...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan resistente...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ rɪˈzɪstənt...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How secure...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan seguro...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ sɪˈkjʊr...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan serio/grave...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How severe...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan severo...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ səˈvɪr...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How stable...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan estable...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈsteɪbəl...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How tricky...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan complicado/delicado...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈtrɪki...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How trustworthy...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan digno de confianza...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈtrʌˌstwɜrði...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How understandable...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan comprensible...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˌʌndərˈstændəbəl...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How widespread...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tan extendido...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ ˈwaɪdˈsprɛd...?</t>
+  </si>
+  <si>
     <t xml:space="preserve">How slow...?</t>
   </si>
   <si>
@@ -501,741 +1236,6 @@
     <t xml:space="preserve">haʊ θɪn...?</t>
   </si>
   <si>
-    <t xml:space="preserve">How warm...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan cálido...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ wɔrm...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How wide...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan ancho...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ waɪd...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How affordable...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan asequible...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ əˈfɔrdəbəl...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How anxious...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan ansioso...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈæŋkʃəs...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How boring...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan aburrido...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈbɔrɪŋ...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How capable...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan capaz...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈkeɪpəbəl...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How confident...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan seguro/confidente...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈkɑnfədənt...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How confusing...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan confuso...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ kənˈfjuzɪŋ...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How curious...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan curioso...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈkjʊriəs...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How dark...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan oscuro...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ dɑrk...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How disappointed...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan decepcionado...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˌdɪsəˈpɔɪntɪd...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How distracted...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan distraído...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ dɪˈstræktɪd...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How embarrassed...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan avergonzado...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ɪmˈbɛrəst...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How energetic...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan enérgico...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˌɛnərˈʤɛtɪk...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How experienced...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan experimentado...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ɪkˈspɪriənst...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How extroverted...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan extrovertido...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈɛkstrəˌvɜrtɪd...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How focused...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan concentrado...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈfoʊkəst...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How friendly...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan amigable...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈfrɛndli...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How frustrated...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan frustrado...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈfrʌˌstreɪtəd...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How grateful...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan agradecido...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈɡreɪtfəl...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How hopeful...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan esperanzado...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈhoʊpfəl...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How hungry...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan hambriento...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈhʌŋɡri...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How inspired...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan inspirado...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ɪnˈspaɪərd...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How interesting...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan interesante...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈɪntrəstɪŋ...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How introverted...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan introvertido...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈɪntroʊˌvɜrtɪd...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How jealous...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan celoso...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈʤɛləs...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How late...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan tarde...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ leɪt...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How lazy...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan perezoso...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈleɪzi...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How likely...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan probable...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈlaɪkli...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto tiempo...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan fuerte (de volumen)...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How motivated...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan motivado...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈmoʊtəˌveɪtəd...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How nervous...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan nervioso...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈnɜrvəs...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How optimistic...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan optimista...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˌɑptəˈmɪstɪk...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How overpriced...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan sobrevalorado/caro...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈoʊvərˌpraɪst...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How overwhelmed...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan abrumado...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˌoʊvərˈwɛlmd...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How patient...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan paciente...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈpeɪʃənt...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How pessimistic...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan pesimista...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˌpɛsəˈmɪstɪk...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How possible...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan posible...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈpɑsəbəl...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How productive...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan productivo...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ prəˈdʌktɪv...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How proud...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan orgulloso...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ praʊd...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan silencioso...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How relieved...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan aliviado...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ rɪˈlivd...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How scared...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan asustado...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ skɛrd...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan poco profundo...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How shy...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan tímido...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ʃaɪ...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How skilled...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan hábil...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ skɪld...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How sleepy...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan somnoliento...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈslipi...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How sociable...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan sociable...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈsoʊʃəbəl...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How soon...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan pronto...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ sun...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How sore...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan adolorido...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ sɔr...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How strong...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan fuerte...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ strɔŋ...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How surprised...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan sorprendido...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ sərˈpraɪzd...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How sweaty...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan sudoroso...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈswɛti...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How talkative...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan hablador...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈtɔkətɪv...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How thirsty...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan sediento...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈθɜrsti...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How weak...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan débil...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ wik...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How accessible...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan accesible...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ækˈsɛsəbəl...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How adaptable...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan adaptable...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ əˈdæptəbəl...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How challenging...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan desafiante...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈʧælənʤɪŋ...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How clear...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan claro...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ klɪr...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How convenient...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan conveniente...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ kənˈvinjənt...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How critical...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan crítico...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈkrɪtɪkəl...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How crucial...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan crucial...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈkruʃəl...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How customizable...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan personalizable...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈkʌstəˌmaɪzəbᵊl...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How demanding...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan exigente...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ dɪˈmændɪŋ...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How durable...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan duradero...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈdʊrəbəl...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How effective...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan efectivo...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ɪˈfɛktɪv...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How efficient...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan eficiente...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ɪˈfɪʃənt...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How essential...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan esencial...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ɪˈsɛnʃəl...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How feasible...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan factible...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈfizəbəl...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How flexible...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan flexible...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈflɛksəbəl...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How influential...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan influyente...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˌɪnfluˈɛnʧəl...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How noticeable...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan notable...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈnoʊtəsəbəl...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How relevant...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan relevante...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈrɛləvənt...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How reliable...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan confiable...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ rɪˈlaɪəbəl...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How resistant...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan resistente...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ rɪˈzɪstənt...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How secure...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan seguro...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ sɪˈkjʊr...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan serio/grave...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How severe...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan severo...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ səˈvɪr...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How stable...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan estable...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈsteɪbəl...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How tricky...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan complicado/delicado...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈtrɪki...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How trustworthy...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan digno de confianza...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈtrʌˌstwɜrði...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How understandable...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan comprensible...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˌʌndərˈstændəbəl...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How widespread...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tan extendido...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ ˈwaɪdˈsprɛd...?</t>
-  </si>
-  <si>
     <t xml:space="preserve">How accurate...?</t>
   </si>
   <si>
@@ -1758,6 +1758,477 @@
     <t xml:space="preserve">haʊ ˈʌɡli...?</t>
   </si>
   <si>
+    <t xml:space="preserve">How much are...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto cuestan...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ɑr...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much attention...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánta atención...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ əˈtɛnʃən...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much can...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto puede...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ kæn...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much change...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto cambio...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ʧeɪnʤ...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much confidence...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánta confianza...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ˈkɑnfədəns...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much control...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto control...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ kənˈtroʊl...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much could...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto podría...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ kʊd...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much damage...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto daño...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ˈdæməʤ...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much detail...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto detalle...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ dɪˈteɪl...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much did...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ dɪd...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much do...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ du...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much does...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ dʌz...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much effort...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto esfuerzo...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ˈɛfərt...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much energy...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánta energía...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ˈɛnərʤi...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much experience...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánta experiencia...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ɪkˈspɪriəns...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much faster...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto más rápido...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ˈfæstər...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much food...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánta comida...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ fud...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much freedom...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánta libertad...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ˈfridəm...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much fun...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto diversión...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ fʌn...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much has...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto ha...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ hæz...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much help...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánta ayuda...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ hɛlp...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much impact...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué tanto impacto...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ˈɪmpækt...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much improvement...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto mejoramiento...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ɪmˈpruvmənt...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much income...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto ingreso...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ˈɪnˌkʌm...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much influence...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánta influencia...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ˈɪnfluəns...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much information...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánta información...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ˌɪnfərˈmeɪʃən...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much interest...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto interés...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ˈɪntrəst...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much involvement...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánta participación...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ɪnˈvɑlvmənt...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much is...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto es...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ɪz...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much knowledge...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto conocimiento...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ˈnɑləʤ...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto más...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much maintenance...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto mantenimiento...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ˈmeɪntənəns...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much money...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto dinero...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ˈmʌni...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much more...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ mɔr...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much noise...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto ruido...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ nɔɪz...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much of...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto de...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ʌv...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much participation...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ pɑrˌtɪsəˈpeɪʃən...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much practice...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánta práctica...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ˈpræktəs...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much pressure...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánta presión...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ˈprɛʃər...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much profit...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto beneficio...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ˈprɑfət...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much progress...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto progreso...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ˈprɑˌɡrɛs...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much risk...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto riesgo...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ rɪsk...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much satisfaction...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánta satisfacción...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ˌsætəˈsfækʃən...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much should...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto debería...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ʃʊd...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much sleep...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto sueño...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ slip...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much space...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto espacio...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ speɪs...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much storage...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto almacenamiento...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ˈstɔrəʤ...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much sugar...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto azúcar...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ˈʃʊɡər...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much support...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto apoyo...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ səˈpɔrt...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much time...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ taɪm...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much water...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánta agua...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ ˈwɔtər...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much weight...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto peso...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ weɪt...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much will...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánta voluntad...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ wɪl...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much work...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto trabajo...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ wɜrk...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much would...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haʊ mʌʧ wʊd...?</t>
+  </si>
+  <si>
     <t xml:space="preserve">How useful...?</t>
   </si>
   <si>
@@ -1819,477 +2290,6 @@
   </si>
   <si>
     <t xml:space="preserve">haʊ wɜrθ ɪt...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much are...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto cuestan...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ɑr...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much attention...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánta atención...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ əˈtɛnʃən...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much can...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto puede...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ kæn...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much change...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto cambio...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ʧeɪnʤ...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much confidence...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánta confianza...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ˈkɑnfədəns...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much control...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto control...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ kənˈtroʊl...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much could...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto podría...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ kʊd...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much damage...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto daño...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ˈdæməʤ...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much detail...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto detalle...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ dɪˈteɪl...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much did...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ dɪd...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much do...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ du...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much does...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ dʌz...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much effort...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto esfuerzo...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ˈɛfərt...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much energy...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánta energía...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ˈɛnərʤi...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much experience...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánta experiencia...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ɪkˈspɪriəns...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much faster...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto más rápido...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ˈfæstər...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much food...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánta comida...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ fud...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much freedom...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánta libertad...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ˈfridəm...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much fun...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto diversión...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ fʌn...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much has...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto ha...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ hæz...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much help...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánta ayuda...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ hɛlp...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much impact...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué tanto impacto...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ˈɪmpækt...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much improvement...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto mejoramiento...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ɪmˈpruvmənt...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much income...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto ingreso...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ˈɪnˌkʌm...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much influence...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánta influencia...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ˈɪnfluəns...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much information...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánta información...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ˌɪnfərˈmeɪʃən...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much interest...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto interés...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ˈɪntrəst...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much involvement...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánta participación...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ɪnˈvɑlvmənt...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much is...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto es...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ɪz...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much knowledge...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto conocimiento...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ˈnɑləʤ...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto más...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much maintenance...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto mantenimiento...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ˈmeɪntənəns...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much money...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto dinero...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ˈmʌni...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much more...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ mɔr...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much noise...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto ruido...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ nɔɪz...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much of...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto de...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ʌv...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much participation...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ pɑrˌtɪsəˈpeɪʃən...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much practice...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánta práctica...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ˈpræktəs...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much pressure...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánta presión...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ˈprɛʃər...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much profit...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto beneficio...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ˈprɑfət...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much progress...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto progreso...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ˈprɑˌɡrɛs...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much risk...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto riesgo...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ rɪsk...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much satisfaction...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánta satisfacción...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ˌsætəˈsfækʃən...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much should...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto debería...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ʃʊd...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much sleep...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto sueño...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ slip...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much space...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto espacio...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ speɪs...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much storage...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto almacenamiento...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ˈstɔrəʤ...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much sugar...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto azúcar...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ˈʃʊɡər...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much support...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto apoyo...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ səˈpɔrt...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much time...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ taɪm...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much water...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánta agua...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ ˈwɔtər...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much weight...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto peso...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ weɪt...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much will...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánta voluntad...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ wɪl...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much work...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuánto trabajo...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ wɜrk...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How much would...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">haʊ mʌʧ wʊd...?</t>
   </si>
   <si>
     <t xml:space="preserve">How many apps...?</t>
@@ -11702,7 +11702,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -11715,23 +11715,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -11846,8 +11829,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F39"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.53"/>
@@ -12127,6 +12110,9 @@
       <c r="D20" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="F20" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
@@ -12391,185 +12377,6 @@
         <v>116</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F52" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -12590,7 +12397,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F49"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46.19"/>
@@ -13148,6 +12955,9 @@
       </c>
       <c r="D40" s="1" t="s">
         <v>1552</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13293,9 +13103,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F50"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="39.81"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="33.17"/>
@@ -13851,6 +13661,9 @@
       </c>
       <c r="D40" s="1" t="s">
         <v>1699</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14010,12 +13823,12 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46.66"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="32.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="32.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="1" width="11.53"/>
   </cols>
   <sheetData>
@@ -14285,9 +14098,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="48.78"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="29.75"/>
@@ -14566,6 +14379,9 @@
       </c>
       <c r="D20" s="1" t="s">
         <v>1816</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14809,7 +14625,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F40"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.08"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38.74"/>
@@ -15088,6 +14904,9 @@
       </c>
       <c r="D20" s="1" t="s">
         <v>1924</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15387,9 +15206,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F144"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="43.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="43.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="35.1"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="45.8"/>
@@ -15669,6 +15488,9 @@
       <c r="D20" s="1" t="s">
         <v>2034</v>
       </c>
+      <c r="F20" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
@@ -16223,6 +16045,9 @@
       <c r="D60" s="1" t="s">
         <v>2130</v>
       </c>
+      <c r="F60" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
@@ -16707,6 +16532,9 @@
       <c r="D95" s="1" t="s">
         <v>2216</v>
       </c>
+      <c r="F95" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
@@ -17330,6 +17158,9 @@
       </c>
       <c r="D140" s="1" t="s">
         <v>2347</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17405,12 +17236,12 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="50.45"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40.89"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="1" width="11.53"/>
   </cols>
   <sheetData>
@@ -17708,7 +17539,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F50"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38.03"/>
@@ -18266,6 +18097,9 @@
       </c>
       <c r="D40" s="1" t="s">
         <v>2527</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18425,7 +18259,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F50"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="57.58"/>
@@ -18983,6 +18817,9 @@
       </c>
       <c r="D40" s="1" t="s">
         <v>2671</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19142,7 +18979,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.11"/>
@@ -19260,11 +19097,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F94"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F107"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="37.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="37.33"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.07"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="1" width="11.53"/>
@@ -19272,24 +19109,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>117</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>157</v>
+        <v>118</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>158</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>159</v>
+        <v>120</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>160</v>
+        <v>121</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>161</v>
+        <v>122</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>6</v>
@@ -19297,13 +19134,13 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>162</v>
+        <v>123</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>163</v>
+        <v>124</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>164</v>
+        <v>125</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>6</v>
@@ -19325,13 +19162,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>6</v>
@@ -19353,13 +19190,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>169</v>
+        <v>130</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>170</v>
+        <v>131</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>6</v>
@@ -19367,13 +19204,13 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>171</v>
+        <v>132</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>172</v>
+        <v>133</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>173</v>
+        <v>134</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>6</v>
@@ -19381,13 +19218,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>174</v>
+        <v>135</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>175</v>
+        <v>136</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>176</v>
+        <v>137</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>6</v>
@@ -19395,13 +19232,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>177</v>
+        <v>138</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>178</v>
+        <v>139</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>6</v>
@@ -19423,13 +19260,13 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>6</v>
@@ -19437,13 +19274,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>183</v>
+        <v>144</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>184</v>
+        <v>145</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>6</v>
@@ -19451,13 +19288,13 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>186</v>
+        <v>147</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>187</v>
+        <v>148</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>188</v>
+        <v>149</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>6</v>
@@ -19479,13 +19316,13 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>189</v>
+        <v>150</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>190</v>
+        <v>151</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>191</v>
+        <v>152</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>6</v>
@@ -19493,13 +19330,13 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>193</v>
+        <v>154</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>194</v>
+        <v>155</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>6</v>
@@ -19507,13 +19344,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>195</v>
+        <v>156</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>196</v>
+        <v>157</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>197</v>
+        <v>158</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>6</v>
@@ -19521,13 +19358,13 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>198</v>
+        <v>159</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>199</v>
+        <v>160</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>200</v>
+        <v>161</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>6</v>
@@ -19535,24 +19372,27 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>201</v>
+        <v>162</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>202</v>
+        <v>163</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>203</v>
+        <v>164</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>204</v>
+        <v>165</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>205</v>
+        <v>166</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>206</v>
+        <v>167</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>6</v>
@@ -19574,13 +19414,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>207</v>
+        <v>168</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>209</v>
+        <v>170</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>6</v>
@@ -19588,13 +19428,13 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>210</v>
+        <v>171</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>6</v>
@@ -19602,13 +19442,13 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>213</v>
+        <v>174</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>214</v>
+        <v>175</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>215</v>
+        <v>176</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>6</v>
@@ -19616,13 +19456,13 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>216</v>
+        <v>177</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>218</v>
+        <v>179</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>6</v>
@@ -19630,13 +19470,13 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>219</v>
+        <v>180</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>220</v>
+        <v>181</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>221</v>
+        <v>182</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>6</v>
@@ -19644,13 +19484,13 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>222</v>
+        <v>183</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>223</v>
+        <v>184</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>224</v>
+        <v>185</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>6</v>
@@ -19658,13 +19498,13 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>225</v>
+        <v>186</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>226</v>
+        <v>187</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>227</v>
+        <v>188</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>6</v>
@@ -19672,13 +19512,13 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>229</v>
+        <v>190</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>230</v>
+        <v>191</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>6</v>
@@ -19686,13 +19526,13 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>232</v>
+        <v>193</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>6</v>
@@ -19700,13 +19540,13 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>6</v>
@@ -19717,7 +19557,7 @@
         <v>78</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>80</v>
@@ -19731,7 +19571,7 @@
         <v>81</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>83</v>
@@ -19742,13 +19582,13 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>239</v>
+        <v>200</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>240</v>
+        <v>201</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>241</v>
+        <v>202</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>6</v>
@@ -19770,13 +19610,13 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>242</v>
+        <v>203</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>243</v>
+        <v>204</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>244</v>
+        <v>205</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>6</v>
@@ -19784,13 +19624,13 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>245</v>
+        <v>206</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>246</v>
+        <v>207</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>6</v>
@@ -19798,13 +19638,13 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>248</v>
+        <v>209</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>249</v>
+        <v>210</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>250</v>
+        <v>211</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>6</v>
@@ -19812,24 +19652,24 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>251</v>
+        <v>212</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>252</v>
+        <v>213</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>253</v>
+        <v>214</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>254</v>
+        <v>215</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>255</v>
+        <v>216</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>256</v>
+        <v>217</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>6</v>
@@ -19837,13 +19677,13 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>257</v>
+        <v>218</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>258</v>
+        <v>219</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>259</v>
+        <v>220</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>6</v>
@@ -19851,13 +19691,13 @@
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>260</v>
+        <v>221</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>261</v>
+        <v>222</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>262</v>
+        <v>223</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>6</v>
@@ -19865,13 +19705,13 @@
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>263</v>
+        <v>224</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>264</v>
+        <v>225</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>265</v>
+        <v>226</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>6</v>
@@ -19879,13 +19719,13 @@
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>266</v>
+        <v>227</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>267</v>
+        <v>228</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>268</v>
+        <v>229</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>6</v>
@@ -19896,7 +19736,7 @@
         <v>90</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>269</v>
+        <v>230</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>92</v>
@@ -19907,13 +19747,13 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>270</v>
+        <v>231</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>271</v>
+        <v>232</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>272</v>
+        <v>233</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>6</v>
@@ -19921,13 +19761,13 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>273</v>
+        <v>234</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>274</v>
+        <v>235</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>275</v>
+        <v>236</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>6</v>
@@ -19938,7 +19778,7 @@
         <v>108</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>276</v>
+        <v>237</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>110</v>
@@ -19949,13 +19789,13 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>277</v>
+        <v>238</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>278</v>
+        <v>239</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>6</v>
@@ -19963,13 +19803,13 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>280</v>
+        <v>241</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>281</v>
+        <v>242</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>282</v>
+        <v>243</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>6</v>
@@ -19977,13 +19817,13 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>283</v>
+        <v>244</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>284</v>
+        <v>245</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>285</v>
+        <v>246</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>6</v>
@@ -19991,13 +19831,13 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>286</v>
+        <v>247</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>287</v>
+        <v>248</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>288</v>
+        <v>249</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>6</v>
@@ -20005,13 +19845,13 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>289</v>
+        <v>250</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>290</v>
+        <v>251</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>291</v>
+        <v>252</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>6</v>
@@ -20019,13 +19859,13 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>292</v>
+        <v>253</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>293</v>
+        <v>254</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>294</v>
+        <v>255</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>6</v>
@@ -20033,13 +19873,13 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>295</v>
+        <v>256</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>296</v>
+        <v>257</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>297</v>
+        <v>258</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>6</v>
@@ -20047,13 +19887,13 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>298</v>
+        <v>259</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>299</v>
+        <v>260</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>300</v>
+        <v>261</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>6</v>
@@ -20061,13 +19901,13 @@
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>301</v>
+        <v>262</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>302</v>
+        <v>263</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>303</v>
+        <v>264</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>6</v>
@@ -20075,13 +19915,13 @@
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>304</v>
+        <v>265</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>305</v>
+        <v>266</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>306</v>
+        <v>267</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>6</v>
@@ -20089,24 +19929,27 @@
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>307</v>
+        <v>268</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>308</v>
+        <v>269</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>309</v>
+        <v>270</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>150</v>
+        <v>271</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>151</v>
+        <v>272</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>152</v>
+        <v>273</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>6</v>
@@ -20114,13 +19957,13 @@
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>310</v>
+        <v>274</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>311</v>
+        <v>275</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>312</v>
+        <v>276</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>6</v>
@@ -20128,13 +19971,13 @@
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>153</v>
+        <v>277</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>154</v>
+        <v>278</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>155</v>
+        <v>279</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>6</v>
@@ -20142,13 +19985,13 @@
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>313</v>
+        <v>280</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>314</v>
+        <v>281</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>315</v>
+        <v>282</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>6</v>
@@ -20156,13 +19999,13 @@
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>316</v>
+        <v>283</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>317</v>
+        <v>284</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>318</v>
+        <v>285</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>6</v>
@@ -20170,13 +20013,13 @@
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>319</v>
+        <v>286</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>320</v>
+        <v>287</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>321</v>
+        <v>288</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>6</v>
@@ -20184,13 +20027,13 @@
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>322</v>
+        <v>289</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>323</v>
+        <v>290</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>6</v>
@@ -20198,13 +20041,13 @@
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>325</v>
+        <v>292</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>326</v>
+        <v>293</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>327</v>
+        <v>294</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>6</v>
@@ -20212,13 +20055,13 @@
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>328</v>
+        <v>295</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>329</v>
+        <v>296</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>330</v>
+        <v>297</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>6</v>
@@ -20226,13 +20069,13 @@
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>331</v>
+        <v>298</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>332</v>
+        <v>299</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>6</v>
@@ -20240,13 +20083,13 @@
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>335</v>
+        <v>302</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>336</v>
+        <v>303</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>6</v>
@@ -20268,13 +20111,13 @@
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>337</v>
+        <v>304</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>338</v>
+        <v>305</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>339</v>
+        <v>306</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>6</v>
@@ -20282,13 +20125,13 @@
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>340</v>
+        <v>307</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>341</v>
+        <v>308</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>342</v>
+        <v>309</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>6</v>
@@ -20296,13 +20139,13 @@
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>343</v>
+        <v>310</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>344</v>
+        <v>311</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>345</v>
+        <v>312</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>6</v>
@@ -20310,13 +20153,13 @@
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>346</v>
+        <v>313</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>347</v>
+        <v>314</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>348</v>
+        <v>315</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>6</v>
@@ -20324,13 +20167,13 @@
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>349</v>
+        <v>316</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>350</v>
+        <v>317</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>351</v>
+        <v>318</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>6</v>
@@ -20338,13 +20181,13 @@
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>352</v>
+        <v>319</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>353</v>
+        <v>320</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>354</v>
+        <v>321</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>6</v>
@@ -20352,13 +20195,13 @@
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>355</v>
+        <v>322</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>356</v>
+        <v>323</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>357</v>
+        <v>324</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>6</v>
@@ -20366,24 +20209,24 @@
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>358</v>
+        <v>325</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>359</v>
+        <v>326</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>360</v>
+        <v>327</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>361</v>
+        <v>328</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>362</v>
+        <v>329</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>363</v>
+        <v>330</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>6</v>
@@ -20391,13 +20234,13 @@
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>260</v>
+        <v>221</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>261</v>
+        <v>222</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>262</v>
+        <v>223</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>6</v>
@@ -20405,13 +20248,13 @@
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>263</v>
+        <v>224</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>264</v>
+        <v>225</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>265</v>
+        <v>226</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>6</v>
@@ -20419,13 +20262,13 @@
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>364</v>
+        <v>331</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>365</v>
+        <v>332</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>366</v>
+        <v>333</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>6</v>
@@ -20433,13 +20276,13 @@
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>367</v>
+        <v>334</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>368</v>
+        <v>335</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>369</v>
+        <v>336</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>6</v>
@@ -20447,13 +20290,13 @@
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>370</v>
+        <v>337</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>371</v>
+        <v>338</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>372</v>
+        <v>339</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>6</v>
@@ -20461,13 +20304,13 @@
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>373</v>
+        <v>340</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>374</v>
+        <v>341</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>375</v>
+        <v>342</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>6</v>
@@ -20478,7 +20321,7 @@
         <v>102</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>376</v>
+        <v>343</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>104</v>
@@ -20489,13 +20332,13 @@
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>377</v>
+        <v>344</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>378</v>
+        <v>345</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>379</v>
+        <v>346</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>6</v>
@@ -20503,13 +20346,13 @@
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>380</v>
+        <v>347</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>381</v>
+        <v>348</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>382</v>
+        <v>349</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>6</v>
@@ -20517,13 +20360,13 @@
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>383</v>
+        <v>350</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>384</v>
+        <v>351</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>385</v>
+        <v>352</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>6</v>
@@ -20531,13 +20374,13 @@
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>386</v>
+        <v>353</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>387</v>
+        <v>354</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>388</v>
+        <v>355</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>6</v>
@@ -20545,13 +20388,13 @@
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>389</v>
+        <v>356</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>390</v>
+        <v>357</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>391</v>
+        <v>358</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>6</v>
@@ -20559,15 +20402,197 @@
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B105" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="D94" s="1" t="s">
+      <c r="D105" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="F94" s="1" t="s">
+      <c r="F105" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="F107" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -20588,7 +20613,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F50"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="59.93"/>
@@ -21146,6 +21171,9 @@
       </c>
       <c r="D40" s="1" t="s">
         <v>2841</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21305,7 +21333,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="57.79"/>
@@ -21586,6 +21614,9 @@
       </c>
       <c r="D20" s="1" t="s">
         <v>2931</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21675,7 +21706,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="49.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="55.43"/>
@@ -21886,6 +21917,9 @@
       </c>
       <c r="D15" s="1" t="s">
         <v>2991</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22045,7 +22079,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F66"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="44.95"/>
@@ -22327,6 +22361,9 @@
       <c r="D20" s="1" t="s">
         <v>3080</v>
       </c>
+      <c r="F20" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
@@ -22880,6 +22917,9 @@
       </c>
       <c r="D60" s="1" t="s">
         <v>3190</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22983,9 +23023,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F50"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46.23"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="37.03"/>
@@ -23541,6 +23581,9 @@
       </c>
       <c r="D40" s="1" t="s">
         <v>3327</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23700,7 +23743,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F67"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="48.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="57.36"/>
@@ -23982,6 +24025,9 @@
       <c r="D20" s="1" t="s">
         <v>3416</v>
       </c>
+      <c r="F20" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
@@ -24002,7 +24048,7 @@
         <v>3420</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>3421</v>
@@ -24535,6 +24581,9 @@
       </c>
       <c r="D60" s="1" t="s">
         <v>3519</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24652,7 +24701,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F50"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="56.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="59.29"/>
@@ -25210,6 +25259,9 @@
       </c>
       <c r="D40" s="1" t="s">
         <v>3654</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25369,7 +25421,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32.75"/>
@@ -25560,7 +25612,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34.66"/>
@@ -25723,7 +25775,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="35.52"/>
@@ -26004,6 +26056,9 @@
       </c>
       <c r="D20" s="1" t="s">
         <v>3810</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26092,8 +26147,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F79"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.85"/>
@@ -26141,13 +26196,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>319</v>
+        <v>286</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>320</v>
+        <v>287</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>321</v>
+        <v>288</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>6</v>
@@ -26183,13 +26238,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>322</v>
+        <v>289</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>323</v>
+        <v>290</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>6</v>
@@ -26267,13 +26322,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>335</v>
+        <v>302</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>336</v>
+        <v>303</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>6</v>
@@ -26295,13 +26350,13 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>337</v>
+        <v>304</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>338</v>
+        <v>305</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>339</v>
+        <v>306</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>6</v>
@@ -26351,13 +26406,13 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>343</v>
+        <v>310</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>344</v>
+        <v>311</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>345</v>
+        <v>312</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>6</v>
@@ -26365,13 +26420,16 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>346</v>
+        <v>313</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>347</v>
+        <v>314</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>348</v>
+        <v>315</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26474,13 +26532,13 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>201</v>
+        <v>162</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>202</v>
+        <v>163</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>6</v>
@@ -26614,13 +26672,13 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>229</v>
+        <v>190</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>230</v>
+        <v>191</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>6</v>
@@ -26863,13 +26921,13 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>263</v>
+        <v>224</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>264</v>
+        <v>225</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>265</v>
+        <v>226</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>6</v>
@@ -26927,16 +26985,19 @@
       <c r="D60" s="1" t="s">
         <v>533</v>
       </c>
+      <c r="F60" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>367</v>
+        <v>334</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>368</v>
+        <v>335</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>369</v>
+        <v>336</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>6</v>
@@ -27017,7 +27078,7 @@
         <v>108</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>276</v>
+        <v>237</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>110</v>
@@ -27056,13 +27117,13 @@
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>117</v>
+        <v>362</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>118</v>
+        <v>363</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>119</v>
+        <v>364</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>6</v>
@@ -27070,13 +27131,13 @@
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>126</v>
+        <v>371</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>124</v>
+        <v>369</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>128</v>
+        <v>373</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>6</v>
@@ -27098,13 +27159,13 @@
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>289</v>
+        <v>250</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>290</v>
+        <v>251</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>291</v>
+        <v>252</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>6</v>
@@ -27112,13 +27173,13 @@
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>295</v>
+        <v>256</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>555</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>297</v>
+        <v>258</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>6</v>
@@ -27168,13 +27229,13 @@
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>383</v>
+        <v>350</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>565</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>385</v>
+        <v>352</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>6</v>
@@ -27191,101 +27252,6 @@
         <v>568</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="F86" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -27306,7 +27272,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="29.53"/>
@@ -27468,8 +27434,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F62"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.02"/>
@@ -27480,24 +27446,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>590</v>
+        <v>569</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>591</v>
+        <v>570</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>592</v>
+        <v>571</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>593</v>
+        <v>572</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>594</v>
+        <v>573</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>595</v>
+        <v>574</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>6</v>
@@ -27505,13 +27471,13 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>596</v>
+        <v>575</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>597</v>
+        <v>576</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>598</v>
+        <v>577</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>6</v>
@@ -27519,13 +27485,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>599</v>
+        <v>578</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>600</v>
+        <v>579</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>601</v>
+        <v>580</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>6</v>
@@ -27533,13 +27499,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>602</v>
+        <v>581</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>603</v>
+        <v>582</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>604</v>
+        <v>583</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>6</v>
@@ -27547,13 +27513,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>605</v>
+        <v>584</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>606</v>
+        <v>585</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>607</v>
+        <v>586</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>6</v>
@@ -27561,13 +27527,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>608</v>
+        <v>587</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>609</v>
+        <v>588</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>610</v>
+        <v>589</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>6</v>
@@ -27575,13 +27541,13 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>611</v>
+        <v>590</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>612</v>
+        <v>591</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>6</v>
@@ -27589,13 +27555,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>614</v>
+        <v>593</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>615</v>
+        <v>594</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>616</v>
+        <v>595</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>6</v>
@@ -27603,13 +27569,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>619</v>
+        <v>598</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>6</v>
@@ -27617,13 +27583,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>620</v>
+        <v>599</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>621</v>
+        <v>600</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>6</v>
@@ -27631,13 +27597,13 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>622</v>
+        <v>601</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>623</v>
+        <v>602</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>6</v>
@@ -27645,13 +27611,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>624</v>
+        <v>603</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>625</v>
+        <v>604</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>626</v>
+        <v>605</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>6</v>
@@ -27659,13 +27625,13 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>627</v>
+        <v>606</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>628</v>
+        <v>607</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>629</v>
+        <v>608</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>6</v>
@@ -27673,13 +27639,13 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>630</v>
+        <v>609</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>631</v>
+        <v>610</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>632</v>
+        <v>611</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>6</v>
@@ -27687,13 +27653,13 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>633</v>
+        <v>612</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>634</v>
+        <v>613</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>635</v>
+        <v>614</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>6</v>
@@ -27701,13 +27667,13 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>636</v>
+        <v>615</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>637</v>
+        <v>616</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>638</v>
+        <v>617</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>6</v>
@@ -27715,13 +27681,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>639</v>
+        <v>618</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>640</v>
+        <v>619</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>641</v>
+        <v>620</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>6</v>
@@ -27729,13 +27695,13 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>642</v>
+        <v>621</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>643</v>
+        <v>622</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>644</v>
+        <v>623</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>6</v>
@@ -27743,24 +27709,27 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>645</v>
+        <v>624</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>646</v>
+        <v>625</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>647</v>
+        <v>626</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>648</v>
+        <v>627</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>649</v>
+        <v>628</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>650</v>
+        <v>629</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>6</v>
@@ -27768,13 +27737,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>651</v>
+        <v>630</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>652</v>
+        <v>631</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>653</v>
+        <v>632</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>6</v>
@@ -27782,13 +27751,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>654</v>
+        <v>633</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>655</v>
+        <v>634</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>656</v>
+        <v>635</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>6</v>
@@ -27796,13 +27765,13 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>657</v>
+        <v>636</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>658</v>
+        <v>637</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>659</v>
+        <v>638</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>6</v>
@@ -27810,13 +27779,13 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>660</v>
+        <v>639</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>661</v>
+        <v>640</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>662</v>
+        <v>641</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>6</v>
@@ -27824,13 +27793,13 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>663</v>
+        <v>642</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>664</v>
+        <v>643</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>665</v>
+        <v>644</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>6</v>
@@ -27838,13 +27807,13 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>666</v>
+        <v>645</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>667</v>
+        <v>646</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>668</v>
+        <v>647</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>6</v>
@@ -27852,13 +27821,13 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>669</v>
+        <v>648</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>670</v>
+        <v>649</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>671</v>
+        <v>650</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>6</v>
@@ -27866,13 +27835,13 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>672</v>
+        <v>651</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>673</v>
+        <v>652</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>674</v>
+        <v>653</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>6</v>
@@ -27880,13 +27849,13 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>675</v>
+        <v>654</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>676</v>
+        <v>655</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>677</v>
+        <v>656</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>6</v>
@@ -27897,7 +27866,7 @@
         <v>500</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>678</v>
+        <v>657</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>502</v>
@@ -27908,13 +27877,13 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>679</v>
+        <v>658</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>680</v>
+        <v>659</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>681</v>
+        <v>660</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>6</v>
@@ -27922,13 +27891,13 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>682</v>
+        <v>661</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>683</v>
+        <v>662</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>684</v>
+        <v>663</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>6</v>
@@ -27936,13 +27905,13 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>685</v>
+        <v>664</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>678</v>
+        <v>657</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>686</v>
+        <v>665</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>6</v>
@@ -27950,13 +27919,13 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>687</v>
+        <v>666</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>688</v>
+        <v>667</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>689</v>
+        <v>668</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>6</v>
@@ -27964,13 +27933,13 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>690</v>
+        <v>669</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>691</v>
+        <v>670</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>692</v>
+        <v>671</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>6</v>
@@ -27978,13 +27947,13 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>693</v>
+        <v>672</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>670</v>
+        <v>649</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>694</v>
+        <v>673</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>6</v>
@@ -27992,13 +27961,13 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>695</v>
+        <v>674</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>696</v>
+        <v>675</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>697</v>
+        <v>676</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>6</v>
@@ -28006,13 +27975,13 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>698</v>
+        <v>677</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>699</v>
+        <v>678</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>700</v>
+        <v>679</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>6</v>
@@ -28020,24 +27989,24 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>701</v>
+        <v>680</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>702</v>
+        <v>681</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>703</v>
+        <v>682</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>704</v>
+        <v>683</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>705</v>
+        <v>684</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>706</v>
+        <v>685</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>6</v>
@@ -28045,13 +28014,13 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>707</v>
+        <v>686</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>708</v>
+        <v>687</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>709</v>
+        <v>688</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>6</v>
@@ -28059,13 +28028,13 @@
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>710</v>
+        <v>689</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>711</v>
+        <v>690</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>712</v>
+        <v>691</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>6</v>
@@ -28073,13 +28042,13 @@
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>713</v>
+        <v>692</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>714</v>
+        <v>693</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>715</v>
+        <v>694</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>6</v>
@@ -28087,13 +28056,13 @@
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>716</v>
+        <v>695</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>717</v>
+        <v>696</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>718</v>
+        <v>697</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>6</v>
@@ -28101,13 +28070,13 @@
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>719</v>
+        <v>698</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>720</v>
+        <v>699</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>721</v>
+        <v>700</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>6</v>
@@ -28115,13 +28084,13 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>722</v>
+        <v>701</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>723</v>
+        <v>702</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>724</v>
+        <v>703</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>6</v>
@@ -28129,13 +28098,13 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>725</v>
+        <v>704</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>726</v>
+        <v>705</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>727</v>
+        <v>706</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>6</v>
@@ -28143,13 +28112,13 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>728</v>
+        <v>707</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>729</v>
+        <v>708</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>730</v>
+        <v>709</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>6</v>
@@ -28157,13 +28126,13 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>731</v>
+        <v>710</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>732</v>
+        <v>711</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>6</v>
@@ -28171,13 +28140,13 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>733</v>
+        <v>712</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>734</v>
+        <v>713</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>735</v>
+        <v>714</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>6</v>
@@ -28185,13 +28154,13 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>736</v>
+        <v>715</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>737</v>
+        <v>716</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>738</v>
+        <v>717</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>6</v>
@@ -28199,13 +28168,13 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>739</v>
+        <v>718</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>740</v>
+        <v>719</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>741</v>
+        <v>720</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>6</v>
@@ -28213,13 +28182,13 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>742</v>
+        <v>721</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>743</v>
+        <v>722</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>744</v>
+        <v>723</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>6</v>
@@ -28227,15 +28196,113 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="D55" s="1" t="s">
+      <c r="D62" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="F62" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -28256,7 +28323,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F40"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="35.03"/>
@@ -28537,6 +28604,9 @@
       </c>
       <c r="D20" s="1" t="s">
         <v>806</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28836,7 +28906,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.04"/>
@@ -28928,13 +28998,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>624</v>
+        <v>603</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>625</v>
+        <v>604</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>626</v>
+        <v>605</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>6</v>
@@ -28956,13 +29026,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>731</v>
+        <v>710</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>732</v>
+        <v>711</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>6</v>
@@ -29057,7 +29127,7 @@
         <v>882</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>290</v>
+        <v>251</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>883</v>
@@ -29068,13 +29138,13 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>289</v>
+        <v>250</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>290</v>
+        <v>251</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>291</v>
+        <v>252</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>6</v>
@@ -29097,9 +29167,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F63"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="43.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="43.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="39.6"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="32.57"/>
@@ -29378,6 +29448,9 @@
       </c>
       <c r="D20" s="1" t="s">
         <v>943</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29996,7 +30069,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F50"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="33.6"/>
@@ -30275,6 +30348,9 @@
       </c>
       <c r="D20" s="1" t="s">
         <v>1129</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30711,7 +30787,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F74"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.8"/>
@@ -30993,6 +31069,9 @@
       <c r="D20" s="1" t="s">
         <v>1274</v>
       </c>
+      <c r="F20" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
@@ -31546,6 +31625,9 @@
       </c>
       <c r="D60" s="1" t="s">
         <v>1392</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
